--- a/DOSSIES_MULTIFORMATO/ADAF/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/ADAF/dossie.xlsx
@@ -628,12 +628,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024NE0001955</t>
+          <t>2024NE0001957</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>2/2023</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2618.42</v>
+        <v>12580.69</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Contratação de empresa de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB para publicação de informações, notícias, vídeos e imagens via Website, de acordo com o padr</t>
+          <t>SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DO GOVERNO INCLUINDO O ACESSO GERENCIADO À INTERNET. TC: 0002/2023 AD: 01.</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024NE0001957</t>
+          <t>2024NE0001955</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2/2023</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12580.69</v>
+        <v>2618.42</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -711,19 +711,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DO GOVERNO INCLUINDO O ACESSO GERENCIADO À INTERNET. TC: 0002/2023 AD: 01.</t>
+          <t>Contratação de empresa de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB para publicação de informações, notícias, vídeos e imagens via Website, de acordo com o padr</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2022NE0001298</t>
+          <t>2022NE0001301</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17/2018</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24313.9</v>
+        <v>6899.08</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>- 3º Termo Aditivo ao Contrato 017/2018; Portaria de dispensa de licitação nº 316/2018-ADAF, publicada no DOE de 12/11/2018; Parecer Jurídico nº 1302/2021 AJUR/ADAF de 16/12/2021.</t>
+          <t>- 3º TERMO ADITIVO (TA) AO CONTRATO 009/2019; PERÍODO: JULHO-AGOSTO; PROCESSO SIGED 018202.001730/2022; EXTRATO DO CONTRATO Nº 009/2019 NO D.O.E. EM 28/06/2019; NAD Nº 32 DE 28/04/2022; PARECER JURÍDI</t>
         </is>
       </c>
     </row>
@@ -778,12 +778,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2022NE0001301</t>
+          <t>2022NE0001298</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>17/2018</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6899.08</v>
+        <v>24313.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>- 3º TERMO ADITIVO (TA) AO CONTRATO 009/2019; PERÍODO: JULHO-AGOSTO; PROCESSO SIGED 018202.001730/2022; EXTRATO DO CONTRATO Nº 009/2019 NO D.O.E. EM 28/06/2019; NAD Nº 32 DE 28/04/2022; PARECER JURÍDI</t>
+          <t>- 3º Termo Aditivo ao Contrato 017/2018; Portaria de dispensa de licitação nº 316/2018-ADAF, publicada no DOE de 12/11/2018; Parecer Jurídico nº 1302/2021 AJUR/ADAF de 16/12/2021.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2018NE00895</t>
+          <t>2018NE00894</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4/2014</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7990.23</v>
+        <v>19906</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -831,19 +831,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na prestação de Serviços de execução de Sistemas, CFPP - Cadastro de Folha de Pagamento e Licença de Uso de sistemas de Informação para a disponibilização do siste</t>
+          <t>Contratação de empresa especializada na prestação de serviço de infraestrutura de TI compreendendo os serviços de Instalação, Hospedagem de servidores e suporte em sistemas de informação para esta ADA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2018NE00894</t>
+          <t>2018NE00895</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>4/2014</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19906</v>
+        <v>7990.23</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -861,14 +861,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de infraestrutura de TI compreendendo os serviços de Instalação, Hospedagem de servidores e suporte em sistemas de informação para esta ADA</t>
+          <t>Contratação de Empresa Especializada na prestação de Serviços de execução de Sistemas, CFPP - Cadastro de Folha de Pagamento e Licença de Uso de sistemas de Informação para a disponibilização do siste</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2016NE00901</t>
+          <t>2016NE00893</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -887,7 +887,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Anulação de Saldo da NE 00750, devido o Encerramento do Exercício Financeiro, Ref ao TC Nº 004/2014 - 2º TA - PRODAM</t>
+          <t>Anulação de Saldo da NE 00406, devido o Encerramento do Exercício Financeiro, Ref ao TC Nº 004/2014 - 2º TA - PRODAM</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2016NE00893</t>
+          <t>2016NE00901</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anulação de Saldo da NE 00406, devido o Encerramento do Exercício Financeiro, Ref ao TC Nº 004/2014 - 2º TA - PRODAM</t>
+          <t>Anulação de Saldo da NE 00750, devido o Encerramento do Exercício Financeiro, Ref ao TC Nº 004/2014 - 2º TA - PRODAM</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026NE0000225</t>
+          <t>2026NE0000223</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7/2025</t>
+          <t>3/2022</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5014.73</v>
+        <v>6017.59</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1059,19 +1059,19 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de Tecnologia da Informação, fornecido pela PRODAM RH ( Recursos Humanos).</t>
+          <t>Contratação de empresa especializada na prestação de serviços de hospedagem de serviço em Nuvem. TC: 0003/2022 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026NE0000223</t>
+          <t>2026NE0000225</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3/2022</t>
+          <t>7/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6017.59</v>
+        <v>5014.73</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de hospedagem de serviço em Nuvem. TC: 0003/2022 AD: 03.</t>
+          <t>Contratação de empresa especializada na prestação de serviço de Tecnologia da Informação, fornecido pela PRODAM RH ( Recursos Humanos).</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2017NE01612</t>
+          <t>2017NE01633</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>500.89</v>
+        <v>0.01</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1141,14 +1141,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anulação de Saldo da NE 0550/2017, devido o Encerramento do Exercício Financeiro. Conforme orientação técnica Nº 001/2018 - GINS/SEFAZ.</t>
+          <t>Anulação de Saldo da NE 01344/2017, devido o Encerramento do Exercício Financeiro. Conforme orientação técnica Nº 001/2018 - GINS/SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2017NE01621</t>
+          <t>2017NE01653</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1158,7 +1158,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.02</v>
+        <v>3215.37</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1167,14 +1167,14 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Anulação de Saldo da NE 01134/2017, devido o Encerramento do Exercício Financeiro. Conforme orientação técnica Nº 001/2018 - GINS/SEFAZ.</t>
+          <t>Anulação de Saldo da NE 01343/2017, devido o Encerramento do Exercício Financeiro. Conforme orientação técnica Nº 001/2018 - GINS/SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2017NE01645</t>
+          <t>2017NE01652</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>6390.04</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1193,14 +1193,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE 550/2017, Devolução saldo remanescente de pagamento.</t>
+          <t>Anulação de Saldo da NE 01152/2017, devido o Encerramento do Exercício Financeiro. Conforme orientação técnica Nº 001/2018 - GINS/SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2017NE01637</t>
+          <t>2017NE01651</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.01</v>
+        <v>4976.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1219,14 +1219,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anulação de Saldo da NE 01437/2017, devido o Encerramento do Exercício Financeiro. Conforme orientação técnica Nº 001/2018 - GINS/SEFAZ.</t>
+          <t>Anulação de Saldo da NE 0009/2017, devido o Encerramento do Exercício Financeiro. Conforme orientação técnica Nº 001/2018 - GINS/SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2017NE01650</t>
+          <t>2017NE01649</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>17756.58</v>
+        <v>3195.02</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Anulação de Saldo da NE 0424/2017, devido o Encerramento do Exercício Financeiro. Conforme orientação técnica Nº 001/2018 - GINS/SEFAZ.</t>
+          <t>Anulação de Saldo da NE 0213/2017, devido o Encerramento do Exercício Financeiro. Conforme orientação técnica Nº 001/2018 - GINS/SEFAZ.</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2017NE01649</t>
+          <t>2017NE01650</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3195.02</v>
+        <v>17756.58</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1297,14 +1297,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anulação de Saldo da NE 0213/2017, devido o Encerramento do Exercício Financeiro. Conforme orientação técnica Nº 001/2018 - GINS/SEFAZ.</t>
+          <t>Anulação de Saldo da NE 0424/2017, devido o Encerramento do Exercício Financeiro. Conforme orientação técnica Nº 001/2018 - GINS/SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2017NE01651</t>
+          <t>2017NE01637</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4976.5</v>
+        <v>0.01</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1323,14 +1323,14 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Anulação de Saldo da NE 0009/2017, devido o Encerramento do Exercício Financeiro. Conforme orientação técnica Nº 001/2018 - GINS/SEFAZ.</t>
+          <t>Anulação de Saldo da NE 01437/2017, devido o Encerramento do Exercício Financeiro. Conforme orientação técnica Nº 001/2018 - GINS/SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2017NE01652</t>
+          <t>2017NE01645</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6390.04</v>
+        <v>50</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1349,14 +1349,14 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Anulação de Saldo da NE 01152/2017, devido o Encerramento do Exercício Financeiro. Conforme orientação técnica Nº 001/2018 - GINS/SEFAZ.</t>
+          <t>Anulação parcial da NE 550/2017, Devolução saldo remanescente de pagamento.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2017NE01653</t>
+          <t>2017NE01621</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3215.37</v>
+        <v>0.02</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1375,14 +1375,14 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anulação de Saldo da NE 01343/2017, devido o Encerramento do Exercício Financeiro. Conforme orientação técnica Nº 001/2018 - GINS/SEFAZ.</t>
+          <t>Anulação de Saldo da NE 01134/2017, devido o Encerramento do Exercício Financeiro. Conforme orientação técnica Nº 001/2018 - GINS/SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2017NE01633</t>
+          <t>2017NE01612</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.01</v>
+        <v>500.89</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Anulação de Saldo da NE 01344/2017, devido o Encerramento do Exercício Financeiro. Conforme orientação técnica Nº 001/2018 - GINS/SEFAZ.</t>
+          <t>Anulação de Saldo da NE 0550/2017, devido o Encerramento do Exercício Financeiro. Conforme orientação técnica Nº 001/2018 - GINS/SEFAZ.</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1438,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2024NE0001913</t>
+          <t>2024NE0001914</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>2/2023</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5236.84</v>
+        <v>25161.38</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Contratação de empresa de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB para publicação de informações, notícias, vídeos e imagens via Website, de acordo com o padr</t>
+          <t>SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DO GOVERNO INCLUINDO O ACESSO GERENCIADO À INTERNET. TC: 0002/2023 AD: 01.</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1498,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2024NE0001914</t>
+          <t>2024NE0001913</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2/2023</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>25161.38</v>
+        <v>5236.84</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1521,14 +1521,14 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DO GOVERNO INCLUINDO O ACESSO GERENCIADO À INTERNET. TC: 0002/2023 AD: 01.</t>
+          <t>Contratação de empresa de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB para publicação de informações, notícias, vídeos e imagens via Website, de acordo com o padr</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2018NE01598</t>
+          <t>2018NE01599</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12780.08</v>
+        <v>7849.12</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1547,14 +1547,14 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anulação da NE Nº00317/2018, para ajuste orçamentário e em cumprimento ao art. 42 da LRF.</t>
+          <t>Anulação da NE Nº00894/2018, para ajuste orçamentário e em cumprimento ao art. 42 da LRF.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2018NE01600</t>
+          <t>2018NE01590</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2713.88</v>
+        <v>0.05</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1573,14 +1573,14 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anulação da NE Nº01246/2018, para ajuste orçamentário e em cumprimento ao art. 42 da LRF.</t>
+          <t>Anulação da NE Nº0320/2018, para ajuste orçamentário e em cumprimento ao art. 42 da LRF.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2018NE01601</t>
+          <t>2018NE01591</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9953</v>
+        <v>0.01</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1599,14 +1599,14 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anulação da NE Nº01542/2018, para ajuste orçamentário e em cumprimento ao art. 42 da LRF.</t>
+          <t>Anulação da NE Nº0895/2018, para ajuste orçamentário e em cumprimento ao art. 42 da LRF.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2018NE01591</t>
+          <t>2018NE01601</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.01</v>
+        <v>9953</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1625,14 +1625,14 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anulação da NE Nº0895/2018, para ajuste orçamentário e em cumprimento ao art. 42 da LRF.</t>
+          <t>Anulação da NE Nº01542/2018, para ajuste orçamentário e em cumprimento ao art. 42 da LRF.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2018NE01590</t>
+          <t>2018NE01600</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.05</v>
+        <v>2713.88</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1651,14 +1651,14 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anulação da NE Nº0320/2018, para ajuste orçamentário e em cumprimento ao art. 42 da LRF.</t>
+          <t>Anulação da NE Nº01246/2018, para ajuste orçamentário e em cumprimento ao art. 42 da LRF.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2018NE01599</t>
+          <t>2018NE01598</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>7849.12</v>
+        <v>12780.08</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Anulação da NE Nº00894/2018, para ajuste orçamentário e em cumprimento ao art. 42 da LRF.</t>
+          <t>Anulação da NE Nº00317/2018, para ajuste orçamentário e em cumprimento ao art. 42 da LRF.</t>
         </is>
       </c>
     </row>
@@ -1714,12 +1714,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2018NE01246</t>
+          <t>2018NE01244</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>4/2014</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4976.5</v>
+        <v>1984.15</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1737,19 +1737,19 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de infraestrutura de TI compreendendo os serviços de Instalação, Hospedagem de servidores e suporte em sistemas de informação para esta ADA</t>
+          <t>Contratação de Empresa Especializada na prestação de Serviços de execução de Sistemas, CFPP - Cadastro de Folha de Pagamento e Licença de Uso de sistemas de Informação para a disponibilização do siste</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2018NE01244</t>
+          <t>2018NE01246</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4/2014</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1984.15</v>
+        <v>4976.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1767,19 +1767,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na prestação de Serviços de execução de Sistemas, CFPP - Cadastro de Folha de Pagamento e Licença de Uso de sistemas de Informação para a disponibilização do siste</t>
+          <t>Contratação de empresa especializada na prestação de serviço de infraestrutura de TI compreendendo os serviços de Instalação, Hospedagem de servidores e suporte em sistemas de informação para esta ADA</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2020NE00535</t>
+          <t>2020NE00508</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>9184.77</v>
+        <v>18939.59</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1804,12 +1804,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2020NE00508</t>
+          <t>2020NE00535</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>18939.59</v>
+        <v>9184.77</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1834,12 +1834,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2019NE00559</t>
+          <t>2019NE00558</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1312.11</v>
+        <v>3964.12</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1857,19 +1857,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Contratação de empresa para a prestação de serviço de protocolo em plataforma Web (SPROWEB), objetivando o controle e acompanhamento do registro de todos os documentos ou processos do Contratante.</t>
+          <t>Contratação de empresa para prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e folha de pagamento de pessoal, processar folhas de pagamento e fornecer rel</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2019NE00558</t>
+          <t>2019NE00559</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3964.12</v>
+        <v>1312.11</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e folha de pagamento de pessoal, processar folhas de pagamento e fornecer rel</t>
+          <t>Contratação de empresa para a prestação de serviço de protocolo em plataforma Web (SPROWEB), objetivando o controle e acompanhamento do registro de todos os documentos ou processos do Contratante.</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2019NE01309</t>
+          <t>2019NE01315</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.05</v>
+        <v>11295.56</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2003,14 +2003,14 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anulação da NE Nº00017/2019, para ajuste orçamentário, de encerramento do exercício de 2019, conforme o Decreto Nº 41.554, de 26 de Novembro de 2019.</t>
+          <t>Anulação da NE Nº00715/2019, para ajuste orçamentário, de encerramento do exercício de 2019, conforme o Decreto Nº 41.554, de 26 de Novembro de 2019.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2019NE01339</t>
+          <t>2019NE01312</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2479.64</v>
+        <v>30.78</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2029,14 +2029,14 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE Nº01057/2019, para ajuste orçamentário, de encerramento do exercício de 2019, conforme o Decreto Nº 41.554, de 26 de Novembro de 2019.</t>
+          <t>Anulação da NE Nº00559/2019, para ajuste orçamentário, de encerramento do exercício de 2019, conforme o Decreto Nº 41.554, de 26 de Novembro de 2019.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2019NE01310</t>
+          <t>2019NE01340</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11190.2</v>
+        <v>4981.62</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2055,14 +2055,14 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Anulação da NE Nº00026/2019, para ajuste orçamentário, de encerramento do exercício de 2019, conforme o Decreto Nº 41.554, de 26 de Novembro de 2019.</t>
+          <t>Anulação parcial da NE Nº01061/2019, para ajuste orçamentário, de encerramento do exercício de 2019, conforme o Decreto Nº 41.554, de 26 de Novembro de 2019.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2019NE01311</t>
+          <t>2019NE01314</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1454.12</v>
+        <v>25.14</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2081,14 +2081,14 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Anulação da NE Nº00558/2019, para ajuste orçamentário, de encerramento do exercício de 2019, conforme o Decreto Nº 41.554, de 26 de Novembro de 2019.</t>
+          <t>Anulação da NE Nº00706/2019, para ajuste orçamentário, de encerramento do exercício de 2019, conforme o Decreto Nº 41.554, de 26 de Novembro de 2019.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2019NE01316</t>
+          <t>2019NE01338</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2479.64</v>
+        <v>2638.82</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Anulação da NE Nº01067/2019, para ajuste orçamentário, de encerramento do exercício de 2019, conforme o Decreto Nº 41.554, de 26 de Novembro de 2019.</t>
+          <t>Anulação parcial da NE Nº01036/2019, para ajuste orçamentário, de encerramento do exercício de 2019, conforme o Decreto Nº 41.554, de 26 de Novembro de 2019.</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2019NE01338</t>
+          <t>2019NE01316</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2638.82</v>
+        <v>2479.64</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2159,14 +2159,14 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE Nº01036/2019, para ajuste orçamentário, de encerramento do exercício de 2019, conforme o Decreto Nº 41.554, de 26 de Novembro de 2019.</t>
+          <t>Anulação da NE Nº01067/2019, para ajuste orçamentário, de encerramento do exercício de 2019, conforme o Decreto Nº 41.554, de 26 de Novembro de 2019.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2019NE01314</t>
+          <t>2019NE01311</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>25.14</v>
+        <v>1454.12</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2185,14 +2185,14 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Anulação da NE Nº00706/2019, para ajuste orçamentário, de encerramento do exercício de 2019, conforme o Decreto Nº 41.554, de 26 de Novembro de 2019.</t>
+          <t>Anulação da NE Nº00558/2019, para ajuste orçamentário, de encerramento do exercício de 2019, conforme o Decreto Nº 41.554, de 26 de Novembro de 2019.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2019NE01340</t>
+          <t>2019NE01310</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4981.62</v>
+        <v>11190.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2211,14 +2211,14 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE Nº01061/2019, para ajuste orçamentário, de encerramento do exercício de 2019, conforme o Decreto Nº 41.554, de 26 de Novembro de 2019.</t>
+          <t>Anulação da NE Nº00026/2019, para ajuste orçamentário, de encerramento do exercício de 2019, conforme o Decreto Nº 41.554, de 26 de Novembro de 2019.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2019NE01312</t>
+          <t>2019NE01339</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>30.78</v>
+        <v>2479.64</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2237,14 +2237,14 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anulação da NE Nº00559/2019, para ajuste orçamentário, de encerramento do exercício de 2019, conforme o Decreto Nº 41.554, de 26 de Novembro de 2019.</t>
+          <t>Anulação parcial da NE Nº01057/2019, para ajuste orçamentário, de encerramento do exercício de 2019, conforme o Decreto Nº 41.554, de 26 de Novembro de 2019.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2019NE01315</t>
+          <t>2019NE01309</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11295.56</v>
+        <v>0.05</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2263,21 +2263,17 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Anulação da NE Nº00715/2019, para ajuste orçamentário, de encerramento do exercício de 2019, conforme o Decreto Nº 41.554, de 26 de Novembro de 2019.</t>
+          <t>Anulação da NE Nº00017/2019, para ajuste orçamentário, de encerramento do exercício de 2019, conforme o Decreto Nº 41.554, de 26 de Novembro de 2019.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2024NE0000915</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>3/2022</t>
-        </is>
-      </c>
+          <t>2024NE0000912</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>27/05/2024</t>
@@ -2293,17 +2289,21 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇO ESPECIALIZADO EM HOSPEDAGEM DE SERVIÇO EM NUVEM. TC: 0003/2022 AD: 02.</t>
+          <t>ERRO VIGÊNCIA CONTRATO</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2024NE0000912</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
+          <t>2024NE0000915</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>3/2022</t>
+        </is>
+      </c>
       <c r="C62" t="inlineStr">
         <is>
           <t>27/05/2024</t>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ERRO VIGÊNCIA CONTRATO</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇO ESPECIALIZADO EM HOSPEDAGEM DE SERVIÇO EM NUVEM. TC: 0003/2022 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -2476,12 +2476,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2024NE0001108</t>
+          <t>2024NE0001107</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>2/2023</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>5236.84</v>
+        <v>25161.38</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Contratação de empresa de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB para publicação de informações, notícias, vídeos e imagens via Website, de acordo com o padr</t>
+          <t>SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DO GOVERNO INCLUINDO O ACESSO GERENCIADO À INTERNET. TC: 0002/2023 AD: 01.</t>
         </is>
       </c>
     </row>
@@ -2536,12 +2536,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2024NE0001107</t>
+          <t>2024NE0001108</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2/2023</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>25161.38</v>
+        <v>5236.84</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DO GOVERNO INCLUINDO O ACESSO GERENCIADO À INTERNET. TC: 0002/2023 AD: 01.</t>
+          <t>Contratação de empresa de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB para publicação de informações, notícias, vídeos e imagens via Website, de acordo com o padr</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2596,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025NE0001941</t>
+          <t>2025NE0001938</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7/2025</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10562.28</v>
+        <v>2839.41</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2619,14 +2619,14 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de Tecnologia da Informação, fornecido pela PRODAM RH ( Recursos Humanos).</t>
+          <t>Contratação de empresa especializada na prestação de serviço de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB. TC: 0004/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025NE0001940</t>
+          <t>2025NE0001939</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10598</v>
+        <v>12580.69</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2649,14 +2649,14 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso a rede do governo, incluindo o acesso gerenciado a internet. TC: 0002/2023 AD: 02.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso a rede do governo, incluindo o acesso gerenciado a internet. TC: 0002/2023 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025NE0001939</t>
+          <t>2025NE0001940</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12580.69</v>
+        <v>10598</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2679,19 +2679,19 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso a rede do governo, incluindo o acesso gerenciado a internet. TC: 0002/2023 AD: 01.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso a rede do governo, incluindo o acesso gerenciado a internet. TC: 0002/2023 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025NE0001938</t>
+          <t>2025NE0001941</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>7/2025</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2839.41</v>
+        <v>10562.28</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB. TC: 0004/2024 AD: 01.</t>
+          <t>Contratação de empresa especializada na prestação de serviço de Tecnologia da Informação, fornecido pela PRODAM RH ( Recursos Humanos).</t>
         </is>
       </c>
     </row>
@@ -2772,17 +2772,21 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2023NE0001457</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>2023NE0001474</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>3/2022</t>
+        </is>
+      </c>
       <c r="C78" t="inlineStr">
         <is>
           <t>24/08/2023</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>3591.58</v>
+        <v>5511.13</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2791,28 +2795,24 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPENHO PARA AJUSTE ORÇAMENTÁRIO</t>
+          <t xml:space="preserve">Por força deste Contrato a CONTRATADA obriga-se a prestar ao CONTRATANTE os SERVIÇOS ESPECIALIZADOS EM HOSPEDAGEM DO SERVIDOR EM NUVEM, conforme a proposta datada de 31 de janeiro de 2022, constantes </t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2023NE0001474</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>3/2022</t>
-        </is>
-      </c>
+          <t>2023NE0001457</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
           <t>24/08/2023</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5511.13</v>
+        <v>3591.58</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por força deste Contrato a CONTRATADA obriga-se a prestar ao CONTRATANTE os SERVIÇOS ESPECIALIZADOS EM HOSPEDAGEM DO SERVIDOR EM NUVEM, conforme a proposta datada de 31 de janeiro de 2022, constantes </t>
+          <t>ANULAÇÃO DE EMPENHO PARA AJUSTE ORÇAMENTÁRIO</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025NE0000279</t>
+          <t>2025NE0000278</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>3/2022</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2618.42</v>
+        <v>6137.07</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de hospedagem de serviço em Nuvem. TC: 0003/2022 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -2948,12 +2948,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025NE0000278</t>
+          <t>2025NE0000279</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>3/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>6137.07</v>
+        <v>2618.42</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2971,14 +2971,14 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de hospedagem de serviço em Nuvem. TC: 0003/2022 AD: 03.</t>
+          <t>Contratação de empresa especializada na prestação de serviço de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2024NE0000013</t>
+          <t>2024NE0000012</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>24209.44</v>
+        <v>7613.02</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2024NE0000012</t>
+          <t>2024NE0000013</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>7613.02</v>
+        <v>24209.44</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3060,12 +3060,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2017NE01152</t>
+          <t>2017NE01134</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>4/2014</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>9953</v>
+        <v>3894.7</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3083,19 +3083,19 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Contratação de Serviços de Infraestrutura de TI compreendendo os serviços de Instação, Hospedagem de servidores para ADAF</t>
+          <t>Contratação de Empresa Especializada na prestação de Serviços de execução de Sistemas, CFPP - Cadastro de Folha de Pagamento e Licença de Uso de sistemas de Informação para a disponibilização do siste</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2017NE01134</t>
+          <t>2017NE01152</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>4/2014</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>3894.7</v>
+        <v>9953</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na prestação de Serviços de execução de Sistemas, CFPP - Cadastro de Folha de Pagamento e Licença de Uso de sistemas de Informação para a disponibilização do siste</t>
+          <t>Contratação de Serviços de Infraestrutura de TI compreendendo os serviços de Instação, Hospedagem de servidores para ADAF</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2024NE0000007</t>
+          <t>2024NE0000006</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2/2023</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>24209.44</v>
+        <v>7613.02</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3259,19 +3259,19 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DO GOVERNO INCLUINDO O ACESSO GERENCIADO À INTERNET.</t>
+          <t>4° Termo Aditivo com prorrogação de prazo de 12 meses, com reajuste de 1,86% com base no IGPM, ao Contrato nº 009/2019, referente ao Serviços de Sistema PRODAM-RH, acumulado no período de fevereiro/20</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2024NE0000006</t>
+          <t>2024NE0000007</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>2/2023</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>7613.02</v>
+        <v>24209.44</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3289,14 +3289,14 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>4° Termo Aditivo com prorrogação de prazo de 12 meses, com reajuste de 1,86% com base no IGPM, ao Contrato nº 009/2019, referente ao Serviços de Sistema PRODAM-RH, acumulado no período de fevereiro/20</t>
+          <t>SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DO GOVERNO INCLUINDO O ACESSO GERENCIADO À INTERNET.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2015NE00837</t>
+          <t>2015NE00842</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>157.46</v>
+        <v>6856.66</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2015NE00842</t>
+          <t>2015NE00837</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>6856.66</v>
+        <v>157.46</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3528,10 +3528,14 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2025NE0000004</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr"/>
+          <t>2025NE0000003</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2/2023</t>
+        </is>
+      </c>
       <c r="C104" t="inlineStr">
         <is>
           <t>20/01/2025</t>
@@ -3547,21 +3551,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ERRO DATA EMPENHO</t>
+          <t>SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DO GOVERNO INCLUINDO O ACESSO GERENCIADO À INTERNET. TC: 0002/2023 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2025NE0000003</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2/2023</t>
-        </is>
-      </c>
+          <t>2025NE0000004</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
           <t>20/01/2025</t>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DO GOVERNO INCLUINDO O ACESSO GERENCIADO À INTERNET. TC: 0002/2023 AD: 01.</t>
+          <t>ERRO DATA EMPENHO</t>
         </is>
       </c>
     </row>
@@ -3610,12 +3610,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2025NE0001153</t>
+          <t>2025NE0001151</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>3/2022</t>
+          <t>7/2025</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3624,7 +3624,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>6039.95</v>
+        <v>5281.14</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de hospedagem de serviço em Nuvem. TC: 0003/2022 AD: 03.</t>
+          <t>Contratação de empresa especializada na prestação de serviço de Tecnologia da Informação, fornecido pela PRODAM RH ( Recursos Humanos).</t>
         </is>
       </c>
     </row>
@@ -3670,12 +3670,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2025NE0001151</t>
+          <t>2025NE0001153</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>7/2025</t>
+          <t>3/2022</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>5281.14</v>
+        <v>6039.95</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de Tecnologia da Informação, fornecido pela PRODAM RH ( Recursos Humanos).</t>
+          <t>Contratação de empresa especializada na prestação de serviços de hospedagem de serviço em Nuvem. TC: 0003/2022 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -3730,12 +3730,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2023NE0000002</t>
+          <t>2023NE0000005</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>13798.16</v>
+        <v>4671.36</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>- 3º TA CONTRATO 009/2019; VIGÊNCIA: 03/06/2022 - 02/06/2023; OBJETO: SERVIÇO DE SUPORTE (SOFTWARE) DE RH; EXTRATO DO CONTRATO Nº 009/2019 NO D.O.E. EM 28/06/2019; PARECER JURÍDICO Nº 325/2022 DE 16/0</t>
+          <t>- 3º TERMO ADITIVO AO CONTRATO Nº 010/2019; VIGÊNCIA: 03/06/2022 - 02/06/2023; OBJETO: SISTEMA DE PROTOCOLO; PARECER JURÍDICO Nº 326/2022 DE 16/05/2022; EXTRATO DO 3º TERMO ADITIVO, PULICADO NO D.O.E.</t>
         </is>
       </c>
     </row>
@@ -3790,12 +3790,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2023NE0000005</t>
+          <t>2023NE0000002</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>4671.36</v>
+        <v>13798.16</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>- 3º TERMO ADITIVO AO CONTRATO Nº 010/2019; VIGÊNCIA: 03/06/2022 - 02/06/2023; OBJETO: SISTEMA DE PROTOCOLO; PARECER JURÍDICO Nº 326/2022 DE 16/05/2022; EXTRATO DO 3º TERMO ADITIVO, PULICADO NO D.O.E.</t>
+          <t>- 3º TA CONTRATO 009/2019; VIGÊNCIA: 03/06/2022 - 02/06/2023; OBJETO: SERVIÇO DE SUPORTE (SOFTWARE) DE RH; EXTRATO DO CONTRATO Nº 009/2019 NO D.O.E. EM 28/06/2019; PARECER JURÍDICO Nº 325/2022 DE 16/0</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,11 @@
           <t>2016NE00659</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>4/2014</t>
+        </is>
+      </c>
       <c r="C114" t="inlineStr">
         <is>
           <t>18/10/2016</t>
@@ -3849,11 +3853,7 @@
           <t>2016NE00659</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>4/2014</t>
-        </is>
-      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
           <t>18/10/2016</t>
@@ -3876,7 +3876,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2023NE0001085</t>
+          <t>2023NE0001084</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>3806.51</v>
+        <v>5511.13</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3895,14 +3895,14 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>4° Termo Aditivo com prorrogação de prazo de 12 meses, com reajuste de 1,86% com base no IGPM, ao Contrato nº 009/2019, referente ao Serviços de Sistema PRODAM-RH, acumulado no período de fevereiro/20</t>
+          <t xml:space="preserve">Por força deste Contrato a CONTRATADA obriga-se a prestar ao CONTRATANTE os SERVIÇOS ESPECIALIZADOS EM HOSPEDAGEM DO SERVIDOR EM NUVEM, conforme a proposta datada de 31 de janeiro de 2022, constantes </t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2023NE0001084</t>
+          <t>2023NE0001085</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>5511.13</v>
+        <v>3806.51</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3921,17 +3921,21 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por força deste Contrato a CONTRATADA obriga-se a prestar ao CONTRATANTE os SERVIÇOS ESPECIALIZADOS EM HOSPEDAGEM DO SERVIDOR EM NUVEM, conforme a proposta datada de 31 de janeiro de 2022, constantes </t>
+          <t>4° Termo Aditivo com prorrogação de prazo de 12 meses, com reajuste de 1,86% com base no IGPM, ao Contrato nº 009/2019, referente ao Serviços de Sistema PRODAM-RH, acumulado no período de fevereiro/20</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2024NE0001039</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
+          <t>2024NE0001021</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2/2023</t>
+        </is>
+      </c>
       <c r="C118" t="inlineStr">
         <is>
           <t>18/06/2024</t>
@@ -3947,21 +3951,17 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>REPROGRAMAÇÃO</t>
+          <t>SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DO GOVERNO INCLUINDO O ACESSO GERENCIADO À INTERNET. TC: 0002/2023 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2024NE0001021</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>2/2023</t>
-        </is>
-      </c>
+          <t>2024NE0001039</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
           <t>18/06/2024</t>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DO GOVERNO INCLUINDO O ACESSO GERENCIADO À INTERNET. TC: 0002/2023 AD: 01.</t>
+          <t>REPROGRAMAÇÃO</t>
         </is>
       </c>
     </row>
@@ -4040,12 +4040,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2023NE0001772</t>
+          <t>2023NE0001771</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2/2023</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4054,7 +4054,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>12104.72</v>
+        <v>3806.51</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4063,19 +4063,19 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DO GOVERNO INCLUINDO O ACESSO GERENCIADO À INTERNET.</t>
+          <t>4° Termo Aditivo com prorrogação de prazo de 12 meses, com reajuste de 1,86% com base no IGPM, ao Contrato nº 009/2019, referente ao Serviços de Sistema PRODAM-RH, acumulado no período de fevereiro/20</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2023NE0001771</t>
+          <t>2023NE0001772</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>2/2023</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>3806.51</v>
+        <v>12104.72</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>4° Termo Aditivo com prorrogação de prazo de 12 meses, com reajuste de 1,86% com base no IGPM, ao Contrato nº 009/2019, referente ao Serviços de Sistema PRODAM-RH, acumulado no período de fevereiro/20</t>
+          <t>SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DO GOVERNO INCLUINDO O ACESSO GERENCIADO À INTERNET.</t>
         </is>
       </c>
     </row>
@@ -4246,17 +4246,21 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2023NE0000846</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
+          <t>2023NE00850</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2/2023</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr">
         <is>
           <t>14/06/2023</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1167.84</v>
+        <v>12104.72</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4265,7 +4269,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>3º Termo Aditivo com prorrogação de prazo de 12 (doze) meses ao Contrato nº 010/2019 e Supressão de 10,99%, referente ao Sistema de Protocolo em Plataforma Web (SPROWER). TC: 010/2019 AD: 03.</t>
+          <t>Serviços de Acesso à Internet</t>
         </is>
       </c>
     </row>
@@ -4302,21 +4306,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2023NE00850</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>2/2023</t>
-        </is>
-      </c>
+          <t>2023NE0000846</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
           <t>14/06/2023</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>12104.72</v>
+        <v>1167.84</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Serviços de Acesso à Internet</t>
+          <t>3º Termo Aditivo com prorrogação de prazo de 12 (doze) meses ao Contrato nº 010/2019 e Supressão de 10,99%, referente ao Sistema de Protocolo em Plataforma Web (SPROWER). TC: 010/2019 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -4452,12 +4452,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2019NE00714</t>
+          <t>2019NE00715</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>17/2018</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>28157.04</v>
+        <v>13223.88</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4475,19 +4475,19 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Contratação de serviços de acesso a internet por fibra óptica e acesso de gerenciamento a rede mundial.</t>
+          <t>Contratação de serviços de infraestrutura de TI, compreendendo os serviços de instalação e hospedagem de servidores de dados.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2019NE00715</t>
+          <t>2019NE00714</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>17/2018</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>13223.88</v>
+        <v>28157.04</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4505,14 +4505,14 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Contratação de serviços de infraestrutura de TI, compreendendo os serviços de instalação e hospedagem de servidores de dados.</t>
+          <t>Contratação de serviços de acesso a internet por fibra óptica e acesso de gerenciamento a rede mundial.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2016NE00272</t>
+          <t>2016NE00275</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4526,7 +4526,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1702.11</v>
+        <v>2631.03</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4535,14 +4535,14 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Contratação de Prestação de Serviços de Execução de Sistemas - CFPP, Licença de Uso de sistemas de Protocolo em Plataforma Web - Sproweb, Conforme 1º Termo aditivo ao Contrato Nº 004/2014, Ref. a Nove</t>
+          <t>Contratação de Prestação de Serviços de Execução de Sistemas - CFPP, Licença de Uso de sistemas de Protocolo em Plataforma Web - Sproweb, Conforme 1º Termo aditivo ao Contrato Nº 004/2014, Ref. a deze</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2016NE00267</t>
+          <t>2016NE00274</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4556,7 +4556,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1713.61</v>
+        <v>1711.13</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4565,14 +4565,14 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Contratação de Prestação de Serviços de Execução de Sistemas - CFPP, Licença de Uso de sistemas de Protocolo em Plataforma Web - Sproweb, Conforme 1º Termo aditivo ao Contrato Nº 004/2014, Referente a</t>
+          <t>Contratação de Prestação de Serviços de Execução de Sistemas - CFPP, Licença de Uso de sistemas de Protocolo em Plataforma Web - Sproweb, Conforme 1º Termo aditivo ao Contrato Nº 004/2014, Ref. a Outu</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2016NE00270</t>
+          <t>2016NE00273</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2647.57</v>
+        <v>1711.13</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4595,14 +4595,14 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Contratação de Prestação de Serviços de Execução de Sistemas - CFPP, Licença de Uso de sistemas de Protocolo em Plataforma Web - Sproweb, Conforme 1º Termo aditivo ao Contrato Nº 004/2014, Referente a</t>
+          <t>Contratação de Prestação de Serviços de Execução de Sistemas - CFPP, Licença de Uso de sistemas de Protocolo em Plataforma Web - Sproweb,Conforme 1º Termo aditivo ao Contrato Nº 004/2014, Ref. a Setem</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2016NE00266</t>
+          <t>2016NE00271</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>750</v>
+        <v>1713.61</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4625,14 +4625,14 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Contratação de Prestação de Serviços de Execução de Sistemas - CFPP, Licença de Uso de sistemas de Protocolo em Plataforma Web - Sproweb, Conforme Contrato Nº 004/2014, Referente a Maio/2015. NFSe Emi</t>
+          <t>Contratação de Prestação de Serviços de Execução de Sistemas - CFPP, Licença de Uso de sistemas de Protocolo em Plataforma Web - Sproweb, Conforme 1º Termo aditivo ao Contrato Nº 004/2014, Referente a</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2016NE00271</t>
+          <t>2016NE00266</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4646,7 +4646,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1713.61</v>
+        <v>750</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4655,14 +4655,14 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Contratação de Prestação de Serviços de Execução de Sistemas - CFPP, Licença de Uso de sistemas de Protocolo em Plataforma Web - Sproweb, Conforme 1º Termo aditivo ao Contrato Nº 004/2014, Referente a</t>
+          <t>Contratação de Prestação de Serviços de Execução de Sistemas - CFPP, Licença de Uso de sistemas de Protocolo em Plataforma Web - Sproweb, Conforme Contrato Nº 004/2014, Referente a Maio/2015. NFSe Emi</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2016NE00273</t>
+          <t>2016NE00270</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1711.13</v>
+        <v>2647.57</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4685,14 +4685,14 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Contratação de Prestação de Serviços de Execução de Sistemas - CFPP, Licença de Uso de sistemas de Protocolo em Plataforma Web - Sproweb,Conforme 1º Termo aditivo ao Contrato Nº 004/2014, Ref. a Setem</t>
+          <t>Contratação de Prestação de Serviços de Execução de Sistemas - CFPP, Licença de Uso de sistemas de Protocolo em Plataforma Web - Sproweb, Conforme 1º Termo aditivo ao Contrato Nº 004/2014, Referente a</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2016NE00274</t>
+          <t>2016NE00267</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1711.13</v>
+        <v>1713.61</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -4715,14 +4715,14 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Contratação de Prestação de Serviços de Execução de Sistemas - CFPP, Licença de Uso de sistemas de Protocolo em Plataforma Web - Sproweb, Conforme 1º Termo aditivo ao Contrato Nº 004/2014, Ref. a Outu</t>
+          <t>Contratação de Prestação de Serviços de Execução de Sistemas - CFPP, Licença de Uso de sistemas de Protocolo em Plataforma Web - Sproweb, Conforme 1º Termo aditivo ao Contrato Nº 004/2014, Referente a</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2016NE00275</t>
+          <t>2016NE00272</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2631.03</v>
+        <v>1702.11</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -4745,19 +4745,19 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Contratação de Prestação de Serviços de Execução de Sistemas - CFPP, Licença de Uso de sistemas de Protocolo em Plataforma Web - Sproweb, Conforme 1º Termo aditivo ao Contrato Nº 004/2014, Ref. a deze</t>
+          <t>Contratação de Prestação de Serviços de Execução de Sistemas - CFPP, Licença de Uso de sistemas de Protocolo em Plataforma Web - Sproweb, Conforme 1º Termo aditivo ao Contrato Nº 004/2014, Ref. a Nove</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2025NE0000365</t>
+          <t>2025NE0000366</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>3/2022</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>2618.42</v>
+        <v>6039.95</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -4775,19 +4775,19 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de hospedagem de serviço em Nuvem. TC: 0003/2022 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2025NE0000363</t>
+          <t>2025NE0000364</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2/2023</t>
+          <t>7/2025</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>12580.69</v>
+        <v>6562.28</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -4805,19 +4805,19 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso a rede do governo, incluindo o acesso gerenciado a internet. TC: 0002/2023 AD: 01.</t>
+          <t>Contratação de empresa especializada na prestação de serviço de Tecnologia da Informação, fornecido pela PRODAM RH ( Recursos Humanos).</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2025NE0000364</t>
+          <t>2025NE0000363</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>7/2025</t>
+          <t>2/2023</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>6562.28</v>
+        <v>12580.69</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4835,19 +4835,19 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de Tecnologia da Informação, fornecido pela PRODAM RH ( Recursos Humanos).</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso a rede do governo, incluindo o acesso gerenciado a internet. TC: 0002/2023 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2025NE0000366</t>
+          <t>2025NE0000365</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>3/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4856,7 +4856,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>6039.95</v>
+        <v>2618.42</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de hospedagem de serviço em Nuvem. TC: 0003/2022 AD: 03.</t>
+          <t>Contratação de empresa especializada na prestação de serviço de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB.</t>
         </is>
       </c>
     </row>
@@ -5074,12 +5074,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2021NE0000254</t>
+          <t>2021NE0000253</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>17/2018</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5088,7 +5088,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>18763.76</v>
+        <v>39947.28</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>O presente Termo Aditivo tem por objetivo prorrogar o prazo de vigência, a contar de 30/11/2020 a 29/11/2021. Serviço de infraestrutura e suporte em sistemas de informação de instalação e hospedagem d</t>
+          <t xml:space="preserve">Prorrogar o prazo de vigência do Contrato original por mais 12 (doze) meses, com base na Cláusula Oitava a contar de 17/12/2020 a 16/12/2021, e reajustar em 13,02% os valores conforme Cláusula Décima </t>
         </is>
       </c>
     </row>
@@ -5134,12 +5134,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2021NE0000253</t>
+          <t>2021NE0000254</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>17/2018</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>39947.28</v>
+        <v>18763.76</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prorrogar o prazo de vigência do Contrato original por mais 12 (doze) meses, com base na Cláusula Oitava a contar de 17/12/2020 a 16/12/2021, e reajustar em 13,02% os valores conforme Cláusula Décima </t>
+          <t>O presente Termo Aditivo tem por objetivo prorrogar o prazo de vigência, a contar de 30/11/2020 a 29/11/2021. Serviço de infraestrutura e suporte em sistemas de informação de instalação e hospedagem d</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2018NE01542</t>
+          <t>2018NE01487</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>9953</v>
+        <v>4407.96</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5243,24 +5243,28 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>contratação de empresa especializada na prestação de serviço de infraestrutura de TI, compreendendo os serviços de instalação, hospedagem de servidores e suporte em sistema de informação para esta AAD</t>
+          <t>Contratação de empresa especializada na prestação de serviço de infraestrutura de TI compreendendo os serviços de Instalação, Hospedagem de servidores e suporte em sistemas de informação para esta ADA</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2018NE01543</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr"/>
+          <t>2018NE01541</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>17/2018</t>
+        </is>
+      </c>
       <c r="C163" t="inlineStr">
         <is>
           <t>07/12/2018</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>4407.96</v>
+        <v>9385.68</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5269,19 +5273,19 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>anulação da ne 1487 para correção da modalidade</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado à Rede Mundial, via Rede de Governo.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2018NE01490</t>
+          <t>2018NE01544</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>4/2014</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5290,7 +5294,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>6006.08</v>
+        <v>4407.96</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5299,19 +5303,19 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na prestação de Serviços de execução de Sistemas, CFPP - Cadastro de Folha de Pagamento e Licença de Uso de sistemas de Informação para a disponibilização do siste</t>
+          <t>Contratação de empresa especializada na prestação de serviço de infraestrutura de TI compreendendo os serviços de Instalação, Hospedagem de servidores e suporte em sistemas de informação para esta ADA</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2018NE01544</t>
+          <t>2018NE01490</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>4/2014</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5320,7 +5324,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>4407.96</v>
+        <v>6006.08</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5329,28 +5333,24 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de infraestrutura de TI compreendendo os serviços de Instalação, Hospedagem de servidores e suporte em sistemas de informação para esta ADA</t>
+          <t>Contratação de Empresa Especializada na prestação de Serviços de execução de Sistemas, CFPP - Cadastro de Folha de Pagamento e Licença de Uso de sistemas de Informação para a disponibilização do siste</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2018NE01541</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>17/2018</t>
-        </is>
-      </c>
+          <t>2018NE01543</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
           <t>07/12/2018</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>9385.68</v>
+        <v>4407.96</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5359,14 +5359,14 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado à Rede Mundial, via Rede de Governo.</t>
+          <t>anulação da ne 1487 para correção da modalidade</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2018NE01487</t>
+          <t>2018NE01542</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>4407.96</v>
+        <v>9953</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de infraestrutura de TI compreendendo os serviços de Instalação, Hospedagem de servidores e suporte em sistemas de informação para esta ADA</t>
+          <t>contratação de empresa especializada na prestação de serviço de infraestrutura de TI, compreendendo os serviços de instalação, hospedagem de servidores e suporte em sistema de informação para esta AAD</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2025NE0000724</t>
+          <t>2025NE0000722</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>3/2022</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5440,7 +5440,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>2618.42</v>
+        <v>5747.32</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB.</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇO ESPECIALIZADO EM HOSPEDAGEM DE SERVIÇO EM NUVEM. TC: 0003/2022 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -5486,12 +5486,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2025NE0000722</t>
+          <t>2025NE0000724</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>3/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>5747.32</v>
+        <v>2618.42</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5509,19 +5509,19 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇO ESPECIALIZADO EM HOSPEDAGEM DE SERVIÇO EM NUVEM. TC: 0003/2022 AD: 02.</t>
+          <t>Contratação de empresa especializada na prestação de serviço de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2022NE0000483</t>
+          <t>2022NE0000484</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>2970.67</v>
+        <v>1312.11</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Prestação de Serviços de execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e folha de pagamento de pessoal, processar folhas de pagamento e fornecer relatórios para efetivação do p</t>
+          <t>Contratação de empresa especializada para execução de sistema de protocolo web (SPROWEB).</t>
         </is>
       </c>
     </row>
@@ -5576,12 +5576,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2022NE0000484</t>
+          <t>2022NE0000483</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1312.11</v>
+        <v>2970.67</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -5599,14 +5599,14 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para execução de sistema de protocolo web (SPROWEB).</t>
+          <t>Prestação de Serviços de execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e folha de pagamento de pessoal, processar folhas de pagamento e fornecer relatórios para efetivação do p</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2018NE00254</t>
+          <t>2018NE00255</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
@@ -5616,7 +5616,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>9736.75</v>
+        <v>19906</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5625,14 +5625,14 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Anulação da NE 68/2017 , para ajustar a natureza de despesa do contrato Nº 004/2014 - PRODAM</t>
+          <t>Anulação da NE 72/2017 , para ajustar a natureza de despesa do contrato Nº 008/2016 - PRODAM</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2018NE00255</t>
+          <t>2018NE00254</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -5642,7 +5642,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>19906</v>
+        <v>9736.75</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -5651,24 +5651,28 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Anulação da NE 72/2017 , para ajustar a natureza de despesa do contrato Nº 008/2016 - PRODAM</t>
+          <t>Anulação da NE 68/2017 , para ajustar a natureza de despesa do contrato Nº 004/2014 - PRODAM</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2023NE0001830</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr"/>
+          <t>2023NE0001832</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>3/2022</t>
+        </is>
+      </c>
       <c r="C177" t="inlineStr">
         <is>
           <t>06/11/2023</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>12104.72</v>
+        <v>5511.13</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -5677,7 +5681,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DO GOVERNO INCLUINDO O ACESSO GERENCIADO À INTERNET.</t>
+          <t xml:space="preserve">Por força deste Contrato a CONTRATADA obriga-se a prestar ao CONTRATANTE os SERVIÇOS ESPECIALIZADOS EM HOSPEDAGEM DO SERVIDOR EM NUVEM, conforme a proposta datada de 31 de janeiro de 2022, constantes </t>
         </is>
       </c>
     </row>
@@ -5714,21 +5718,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2023NE0001832</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>3/2022</t>
-        </is>
-      </c>
+          <t>2023NE0001830</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr">
         <is>
           <t>06/11/2023</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>5511.13</v>
+        <v>12104.72</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por força deste Contrato a CONTRATADA obriga-se a prestar ao CONTRATANTE os SERVIÇOS ESPECIALIZADOS EM HOSPEDAGEM DO SERVIDOR EM NUVEM, conforme a proposta datada de 31 de janeiro de 2022, constantes </t>
+          <t>SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DO GOVERNO INCLUINDO O ACESSO GERENCIADO À INTERNET.</t>
         </is>
       </c>
     </row>
@@ -5774,12 +5774,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2024NE0000793</t>
+          <t>2024NE0000794</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>3/2022</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>3806.51</v>
+        <v>11537.34</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>4° Termo Aditivo com prorrogação de prazo de 12 meses, com reajuste de 1,86% com base no IGPM, ao Contrato nº 009/2019, referente ao Serviços de Sistema PRODAM-RH, acumulado no período de fevereiro/20</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇO ESPECIALIZADO EM HOSPEDAGEM DE SERVIÇO EM NUVEM. TC: 0003/2022 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -5834,12 +5834,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2024NE0000794</t>
+          <t>2024NE0000793</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>3/2022</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5848,7 +5848,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>11537.34</v>
+        <v>3806.51</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇO ESPECIALIZADO EM HOSPEDAGEM DE SERVIÇO EM NUVEM. TC: 0003/2022 AD: 02.</t>
+          <t>4° Termo Aditivo com prorrogação de prazo de 12 meses, com reajuste de 1,86% com base no IGPM, ao Contrato nº 009/2019, referente ao Serviços de Sistema PRODAM-RH, acumulado no período de fevereiro/20</t>
         </is>
       </c>
     </row>
@@ -5924,12 +5924,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2021NE0000794</t>
+          <t>2021NE0000793</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>17/2018</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5938,7 +5938,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>35114.88</v>
+        <v>14072.82</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prorrogar o prazo de vigência do Contrato original por mais 12 (doze) meses, com base na Cláusula Oitava a contar de 17/12/2020 a 16/12/2021, e reajustar em 13,02% os valores conforme Cláusula Décima </t>
+          <t>O presente Termo Aditivo tem por objetivo prorrogar o prazo de vigência, a contar de 30/11/2020 a 29/11/2021. Serviço de infraestrutura e suporte em sistemas de informação de instalação e hospedagem d</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2021NE0000793</t>
+          <t>2021NE0000794</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>17/2018</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>14072.82</v>
+        <v>35114.88</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>O presente Termo Aditivo tem por objetivo prorrogar o prazo de vigência, a contar de 30/11/2020 a 29/11/2021. Serviço de infraestrutura e suporte em sistemas de informação de instalação e hospedagem d</t>
+          <t xml:space="preserve">Prorrogar o prazo de vigência do Contrato original por mais 12 (doze) meses, com base na Cláusula Oitava a contar de 17/12/2020 a 16/12/2021, e reajustar em 13,02% os valores conforme Cláusula Décima </t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2015NE00149</t>
+          <t>2015NE00175</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
@@ -6063,14 +6063,14 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DE DIVIDA: Folha de Informação nº 0007/2015, Prestação de serviços de execução de sistemas CFPP- Cadastro Folha de Pagamento de Pessoal, Conf contrato nº 004/2014. Faturas: 12106 de 14.</t>
+          <t>ANULAÇÃO DA NE 162, MODALIDADE INCORRETA NA NOTA DE EMPENHO.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2015NE00161</t>
+          <t>2015NE00162</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -6096,7 +6096,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2015NE00162</t>
+          <t>2015NE00161</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -6122,7 +6122,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2015NE00175</t>
+          <t>2015NE00149</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
@@ -6141,19 +6141,19 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE 162, MODALIDADE INCORRETA NA NOTA DE EMPENHO.</t>
+          <t>RECONHECIMENTO DE DIVIDA: Folha de Informação nº 0007/2015, Prestação de serviços de execução de sistemas CFPP- Cadastro Folha de Pagamento de Pessoal, Conf contrato nº 004/2014. Faturas: 12106 de 14.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026NE0000001</t>
+          <t>2026NE0000003</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>7/2025</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6162,7 +6162,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>11357.64</v>
+        <v>10573.9</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6171,14 +6171,14 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB. TC: 0004/2024 AD: 01.</t>
+          <t>Contratação de empresa especializada na prestação de serviço de Tecnologia da Informação, fornecido pela PRODAM RH ( Recursos Humanos). TC: 0007/2025 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026NE0000004</t>
+          <t>2026NE0000005</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6192,7 +6192,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>12079.9</v>
+        <v>12747.22</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6201,19 +6201,19 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de hospedagem de serviço em Nuvem. TC: 0003/2022 AD: 03.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de hospedagem de serviço em Nuvem. TC: 0003/2022 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026NE0000006</t>
+          <t>2026NE0000002</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2/2023</t>
+          <t>7/2025</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>52868.92</v>
+        <v>10562.28</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6231,19 +6231,19 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso a rede do governo, incluindo o acesso gerenciado a internet. TC: 0002/2023 AD: 02.</t>
+          <t>Contratação de empresa especializada na prestação de serviço de Tecnologia da Informação, fornecido pela PRODAM RH ( Recursos Humanos).</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026NE0000002</t>
+          <t>2026NE0000006</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>7/2025</t>
+          <t>2/2023</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6252,7 +6252,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>10562.28</v>
+        <v>52868.92</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6261,14 +6261,14 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de Tecnologia da Informação, fornecido pela PRODAM RH ( Recursos Humanos).</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso a rede do governo, incluindo o acesso gerenciado a internet. TC: 0002/2023 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026NE0000005</t>
+          <t>2026NE0000004</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>12747.22</v>
+        <v>12079.9</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6291,19 +6291,19 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de hospedagem de serviço em Nuvem. TC: 0003/2022 AD: 04.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de hospedagem de serviço em Nuvem. TC: 0003/2022 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026NE0000003</t>
+          <t>2026NE0000001</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>7/2025</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>10573.9</v>
+        <v>11357.64</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6321,14 +6321,14 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de Tecnologia da Informação, fornecido pela PRODAM RH ( Recursos Humanos). TC: 0007/2025 AD: 01.</t>
+          <t>Contratação de empresa especializada na prestação de serviço de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB. TC: 0004/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2015NE00038</t>
+          <t>2015NE00031</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6351,14 +6351,14 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DA NE 31 POR MOTIVO DE CORREÇÃO NA DESCRIÇÃO DA MESMA</t>
+          <t>Contratação de serviços de Processamentos de Dados, como instalação e Configuração de Folha de Pagamento, Sistema de Folha de Pagamento e Sistema SPROWeb para esta Agencia.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2015NE00040</t>
+          <t>2015NE00042</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6418,7 +6418,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2015NE00042</t>
+          <t>2015NE00040</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6448,7 +6448,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2015NE00031</t>
+          <t>2015NE00038</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Contratação de serviços de Processamentos de Dados, como instalação e Configuração de Folha de Pagamento, Sistema de Folha de Pagamento e Sistema SPROWeb para esta Agencia.</t>
+          <t>CANCELAMENTO DA NE 31 POR MOTIVO DE CORREÇÃO NA DESCRIÇÃO DA MESMA</t>
         </is>
       </c>
     </row>
@@ -6624,12 +6624,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026NE0000251</t>
+          <t>2026NE0000245</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>3/2022</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6638,7 +6638,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>2839.41</v>
+        <v>6017.59</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -6647,14 +6647,14 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB. TC: 0004/2024 AD: 01.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de hospedagem de serviço em Nuvem. TC: 0003/2022 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026NE0000250</t>
+          <t>2026NE0000247</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6684,12 +6684,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026NE0000248</t>
+          <t>2026NE0000244</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>3/2022</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>2839.41</v>
+        <v>6017.59</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -6707,19 +6707,19 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB. TC: 0004/2024 AD: 01.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de hospedagem de serviço em Nuvem. TC: 0003/2022 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026NE0000249</t>
+          <t>2026NE0000246</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>3/2022</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>2839.41</v>
+        <v>6017.59</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -6737,19 +6737,19 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB. TC: 0004/2024 AD: 01.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de hospedagem de serviço em Nuvem. TC: 0003/2022 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026NE0000246</t>
+          <t>2026NE0000249</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>3/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>6017.59</v>
+        <v>2839.41</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -6767,19 +6767,19 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de hospedagem de serviço em Nuvem. TC: 0003/2022 AD: 03.</t>
+          <t>Contratação de empresa especializada na prestação de serviço de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB. TC: 0004/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026NE0000244</t>
+          <t>2026NE0000248</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>3/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6788,7 +6788,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>6017.59</v>
+        <v>2839.41</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -6797,14 +6797,14 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de hospedagem de serviço em Nuvem. TC: 0003/2022 AD: 03.</t>
+          <t>Contratação de empresa especializada na prestação de serviço de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB. TC: 0004/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026NE0000247</t>
+          <t>2026NE0000250</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6834,12 +6834,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026NE0000245</t>
+          <t>2026NE0000251</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>3/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>6017.59</v>
+        <v>2839.41</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -6857,14 +6857,14 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de hospedagem de serviço em Nuvem. TC: 0003/2022 AD: 03.</t>
+          <t>Contratação de empresa especializada na prestação de serviço de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo WEB. TC: 0004/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2021NE0000030</t>
+          <t>2021NE0000032</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -6874,7 +6874,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>8809.08</v>
+        <v>39947.28</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -6883,14 +6883,14 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>O presente Termo Aditivo tem por objetivo prorrogar o prazo de vigência do contrato original por mais 12 (doze) meses, a contar de 03/06/2020 a 02/06/2021, com base na cláusula oitava do contrato prim</t>
+          <t xml:space="preserve">Prorrogar o prazo de vigência do Contrato original por mais 12 (doze) meses, com base na Cláusula Oitava a contar de 17/12/2020 a 16/12/2021, e reajustar em 13,02% os valores conforme Cláusula Décima </t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2021NE0000029</t>
+          <t>2021NE0000031</t>
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -6900,7 +6900,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>5248.44</v>
+        <v>18763.76</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -6909,14 +6909,14 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>O presente Termo Aditivo tem por objetivo prorrogar o prazo de vigência do contrato original por mais 12 (doze) meses, a contar de 03/06/2020 a 02/06/2021, com base na cláusula oitava do contrato prim</t>
+          <t>O presente Termo Aditivo tem por objetivo prorrogar o prazo de vigência, a contar de 30/11/2020 a 29/11/2021. Serviço de infraestrutura e suporte em sistemas de informação de instalação e hospedagem d</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2021NE0000031</t>
+          <t>2021NE0000029</t>
         </is>
       </c>
       <c r="B220" t="inlineStr"/>
@@ -6926,7 +6926,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>18763.76</v>
+        <v>5248.44</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -6935,14 +6935,14 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>O presente Termo Aditivo tem por objetivo prorrogar o prazo de vigência, a contar de 30/11/2020 a 29/11/2021. Serviço de infraestrutura e suporte em sistemas de informação de instalação e hospedagem d</t>
+          <t>O presente Termo Aditivo tem por objetivo prorrogar o prazo de vigência do contrato original por mais 12 (doze) meses, a contar de 03/06/2020 a 02/06/2021, com base na cláusula oitava do contrato prim</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2021NE0000032</t>
+          <t>2021NE0000030</t>
         </is>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>39947.28</v>
+        <v>8809.08</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -6961,21 +6961,17 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prorrogar o prazo de vigência do Contrato original por mais 12 (doze) meses, com base na Cláusula Oitava a contar de 17/12/2020 a 16/12/2021, e reajustar em 13,02% os valores conforme Cláusula Décima </t>
+          <t>O presente Termo Aditivo tem por objetivo prorrogar o prazo de vigência do contrato original por mais 12 (doze) meses, a contar de 03/06/2020 a 02/06/2021, com base na cláusula oitava do contrato prim</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2016NE00032</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>4/2014</t>
-        </is>
-      </c>
+          <t>2016NE00033</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
       <c r="C222" t="inlineStr">
         <is>
           <t>04/01/2016</t>
@@ -6991,7 +6987,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Contratação de Serviços de Execução de Sistemas. Referentes a o Sistema CFPP - Cadastro e Folha de Pagamento de Pessoal e Licença do Sproweb.</t>
+          <t>Contratação de Serviços de Execução de Sistemas, Referente ao CFPP - Cadastro e Folha de Pagamento e Licença do Sproweb.</t>
         </is>
       </c>
     </row>
@@ -7028,10 +7024,14 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2016NE00033</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr"/>
+          <t>2016NE00032</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>4/2014</t>
+        </is>
+      </c>
       <c r="C224" t="inlineStr">
         <is>
           <t>04/01/2016</t>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Contratação de Serviços de Execução de Sistemas, Referente ao CFPP - Cadastro e Folha de Pagamento e Licença do Sproweb.</t>
+          <t>Contratação de Serviços de Execução de Sistemas. Referentes a o Sistema CFPP - Cadastro e Folha de Pagamento de Pessoal e Licença do Sproweb.</t>
         </is>
       </c>
     </row>
@@ -7084,12 +7084,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2022NE0000145</t>
+          <t>2022NE0000146</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2/2023</t>
+          <t>3/2022</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7107,19 +7107,19 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>CORREÇÃO</t>
+          <t xml:space="preserve">Por força deste Contrato a CONTRATADA obriga-se a prestar ao CONTRATANTE os SERVIÇOS ESPECIALIZADOS EM HOSPEDAGEM DO SERVIDOR EM NUVEM, conforme a proposta datada de 31 de janeiro de 2022, constantes </t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2022NE0000146</t>
+          <t>2022NE0000145</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>3/2022</t>
+          <t>2/2023</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7137,19 +7137,19 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por força deste Contrato a CONTRATADA obriga-se a prestar ao CONTRATANTE os SERVIÇOS ESPECIALIZADOS EM HOSPEDAGEM DO SERVIDOR EM NUVEM, conforme a proposta datada de 31 de janeiro de 2022, constantes </t>
+          <t>CORREÇÃO</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026NE0000240</t>
+          <t>2026NE0000236</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>7/2025</t>
+          <t>2/2023</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7158,7 +7158,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>2910.07</v>
+        <v>13217.1</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -7167,14 +7167,14 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de Tecnologia da Informação, fornecido pela PRODAM RH ( Recursos Humanos).</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso a rede do governo, incluindo o acesso gerenciado a internet. TC: 0002/2023 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026NE0000237</t>
+          <t>2026NE0000235</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -7204,12 +7204,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026NE0000241</t>
+          <t>2026NE0000238</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>7/2025</t>
+          <t>2/2023</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>2889.02</v>
+        <v>13217.1</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de Tecnologia da Informação, fornecido pela PRODAM RH ( Recursos Humanos).</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso a rede do governo, incluindo o acesso gerenciado a internet. TC: 0002/2023 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -7264,12 +7264,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026NE0000238</t>
+          <t>2026NE0000241</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2/2023</t>
+          <t>7/2025</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>13217.1</v>
+        <v>2889.02</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7287,14 +7287,14 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso a rede do governo, incluindo o acesso gerenciado a internet. TC: 0002/2023 AD: 02.</t>
+          <t>Contratação de empresa especializada na prestação de serviço de Tecnologia da Informação, fornecido pela PRODAM RH ( Recursos Humanos).</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026NE0000235</t>
+          <t>2026NE0000237</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -7324,12 +7324,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026NE0000236</t>
+          <t>2026NE0000240</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2/2023</t>
+          <t>7/2025</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7338,7 +7338,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>13217.1</v>
+        <v>2910.07</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso a rede do governo, incluindo o acesso gerenciado a internet. TC: 0002/2023 AD: 02.</t>
+          <t>Contratação de empresa especializada na prestação de serviço de Tecnologia da Informação, fornecido pela PRODAM RH ( Recursos Humanos).</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2019NE01061</t>
+          <t>2019NE01060</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>9987.32</v>
+        <v>18771.36</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7407,14 +7407,14 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>O presente Termo Aditivo tem por objetivo prorrogar o prazo de vigência do contrato original por mais 12 (doze) meses, com base na Cláusula Oitava a contar de 17/12/2019 a 16/12/2020, e reajustar em 6</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado á Rede Mundial, via Rede de Governo.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2019NE01060</t>
+          <t>2019NE01061</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>18771.36</v>
+        <v>9987.32</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado á Rede Mundial, via Rede de Governo.</t>
+          <t>O presente Termo Aditivo tem por objetivo prorrogar o prazo de vigência do contrato original por mais 12 (doze) meses, com base na Cláusula Oitava a contar de 17/12/2019 a 16/12/2020, e reajustar em 6</t>
         </is>
       </c>
     </row>
@@ -7500,12 +7500,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2025NE0000007</t>
+          <t>2025NE0000005</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2/2023</t>
+          <t>3/2022</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7514,7 +7514,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>25161.38</v>
+        <v>11537.34</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DO GOVERNO INCLUINDO O ACESSO GERENCIADO À INTERNET. TC: 0002/2023 AD: 01.</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇO ESPECIALIZADO EM HOSPEDAGEM DE SERVIÇO EM NUVEM. TC: 0003/2022 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -7560,12 +7560,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2025NE0000005</t>
+          <t>2025NE0000007</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>3/2022</t>
+          <t>2/2023</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -7574,7 +7574,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>11537.34</v>
+        <v>25161.38</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -7583,19 +7583,19 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇO ESPECIALIZADO EM HOSPEDAGEM DE SERVIÇO EM NUVEM. TC: 0003/2022 AD: 02.</t>
+          <t>SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DO GOVERNO INCLUINDO O ACESSO GERENCIADO À INTERNET. TC: 0002/2023 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2024NE0000017</t>
+          <t>2024NE0000062</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>3/2022</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -7604,7 +7604,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>7613.02</v>
+        <v>5511.13</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>4° Termo Aditivo com prorrogação de prazo de 12 meses, com reajuste de 1,86% com base no IGPM, ao Contrato nº 009/2019, referente ao Serviços de Sistema PRODAM-RH, acumulado no período de fevereiro/20</t>
+          <t xml:space="preserve">Por força deste Contrato a CONTRATADA obriga-se a prestar ao CONTRATANTE os SERVIÇOS ESPECIALIZADOS EM HOSPEDAGEM DO SERVIDOR EM NUVEM, conforme a proposta datada de 31 de janeiro de 2022, constantes </t>
         </is>
       </c>
     </row>
@@ -7650,12 +7650,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2024NE0000062</t>
+          <t>2024NE0000017</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>3/2022</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7664,7 +7664,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>5511.13</v>
+        <v>7613.02</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -7673,19 +7673,19 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por força deste Contrato a CONTRATADA obriga-se a prestar ao CONTRATANTE os SERVIÇOS ESPECIALIZADOS EM HOSPEDAGEM DO SERVIDOR EM NUVEM, conforme a proposta datada de 31 de janeiro de 2022, constantes </t>
+          <t>4° Termo Aditivo com prorrogação de prazo de 12 meses, com reajuste de 1,86% com base no IGPM, ao Contrato nº 009/2019, referente ao Serviços de Sistema PRODAM-RH, acumulado no período de fevereiro/20</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2020NE00024</t>
+          <t>2020NE00009</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>17/2018</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>115187.09</v>
+        <v>11011.35</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -7703,19 +7703,19 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>O presente Termo Aditivo tem por objetivo prorrogar o prazo de vigência do contrato original por mais 12 (doze) meses, com base na Cláusula Oitava a contar de 17/12/2019 a 16/12/2020, e reajustar em 6</t>
+          <t>Contratação de empresa para prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e folha de pagamento de pessoal, processar folhas de pagamento e fornecer rel</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2020NE00006</t>
+          <t>2020NE00010</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7724,7 +7724,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>6560.55</v>
+        <v>51600.34</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -7733,19 +7733,19 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Contratação de empresa para a prestação de serviço de protocolo em plataforma Web (SPROWEB), objetivando o controle e acompanhamento do registro de todos os documentos ou processos do Contratante.</t>
+          <t>O presente Termo Aditivo tem por objetivo prorrogar o prazo de vigência do contrato original por mais 12 (doze) meses, com base na Cláusula Nona a contar de 30/11/2019 a 29/11/2020, e reajustar em 6,4</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2020NE00010</t>
+          <t>2020NE00006</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7754,7 +7754,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>51600.34</v>
+        <v>6560.55</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -7763,19 +7763,19 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>O presente Termo Aditivo tem por objetivo prorrogar o prazo de vigência do contrato original por mais 12 (doze) meses, com base na Cláusula Nona a contar de 30/11/2019 a 29/11/2020, e reajustar em 6,4</t>
+          <t>Contratação de empresa para a prestação de serviço de protocolo em plataforma Web (SPROWEB), objetivando o controle e acompanhamento do registro de todos os documentos ou processos do Contratante.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2020NE00009</t>
+          <t>2020NE00024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>17/2018</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>11011.35</v>
+        <v>115187.09</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -7793,19 +7793,19 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e folha de pagamento de pessoal, processar folhas de pagamento e fornecer rel</t>
+          <t>O presente Termo Aditivo tem por objetivo prorrogar o prazo de vigência do contrato original por mais 12 (doze) meses, com base na Cláusula Oitava a contar de 17/12/2019 a 16/12/2020, e reajustar em 6</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2019NE00026</t>
+          <t>2019NE00020</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>17/2018</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>13223.88</v>
+        <v>28157.04</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de infraestrutura de TI compreendendo os serviços de Instalação, Hospedagem de servidores e suporte em sistemas de informação para esta ADA</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado á Rede Mundial, via Rede de Governo.</t>
         </is>
       </c>
     </row>
@@ -7860,12 +7860,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2019NE00020</t>
+          <t>2019NE00026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>17/2018</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7874,7 +7874,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>28157.04</v>
+        <v>13223.88</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -7883,24 +7883,28 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado á Rede Mundial, via Rede de Governo.</t>
+          <t>Contratação de empresa especializada na prestação de serviço de infraestrutura de TI compreendendo os serviços de Instalação, Hospedagem de servidores e suporte em sistemas de informação para esta ADA</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2018NE00066</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr"/>
+          <t>2018NE00072</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>8/2016</t>
+        </is>
+      </c>
       <c r="C253" t="inlineStr">
         <is>
           <t>02/01/2018</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>9736.75</v>
+        <v>19906</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -7909,14 +7913,14 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Anulação da NE 62/2017, emitida em 02.01.2018, devido a necessidade de corrigir a descrição da Nota de Empenho.</t>
+          <t>Contratação de empresa especializada na prestação de serviço de infraestrutura de TI compreendendo os serviços de Instalação, Hospedagem de servidores e suporte em sistemas de informação para esta ADA</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2018NE00068</t>
+          <t>2018NE00062</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7946,7 +7950,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2018NE00062</t>
+          <t>2018NE00068</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7976,21 +7980,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2018NE00072</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>8/2016</t>
-        </is>
-      </c>
+          <t>2018NE00066</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
       <c r="C256" t="inlineStr">
         <is>
           <t>02/01/2018</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>19906</v>
+        <v>9736.75</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -7999,19 +7999,19 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de infraestrutura de TI compreendendo os serviços de Instalação, Hospedagem de servidores e suporte em sistemas de informação para esta ADA</t>
+          <t>Anulação da NE 62/2017, emitida em 02.01.2018, devido a necessidade de corrigir a descrição da Nota de Empenho.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2017NE00009</t>
+          <t>2017NE00005</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>4/2014</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8020,7 +8020,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>4976.5</v>
+        <v>7535.44</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -8029,19 +8029,19 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Contratação de Serviços de Infraestrutura de TI compreendendo os serviços de Instação, Hospedagem de servidores para ADAF</t>
+          <t>Contratação de Empresa Especializada na prestação de Serviços de execução de Sistemas, CFPP - Cadastro de Folha de Pagamento e Licença de Uso de sistemas de Informação para a disponibilização do siste</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2017NE00005</t>
+          <t>2017NE00009</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>4/2014</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>7535.44</v>
+        <v>4976.5</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na prestação de Serviços de execução de Sistemas, CFPP - Cadastro de Folha de Pagamento e Licença de Uso de sistemas de Informação para a disponibilização do siste</t>
+          <t>Contratação de Serviços de Infraestrutura de TI compreendendo os serviços de Instação, Hospedagem de servidores para ADAF</t>
         </is>
       </c>
     </row>
@@ -8096,12 +8096,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2022NE0001591</t>
+          <t>2022NE0001590</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1167.84</v>
+        <v>3449.54</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -8119,19 +8119,19 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>- 3º TERMO ADITIVO AO CONTRATO Nº 010/2019; VALOR GLOBAL: R$ 14.014,08; VIGÊNCIA: 03/06/2022 - 02/06/2023; NOTA DE AUTORIZAÇÃO DE DESPESAS (NAD) Nº 39 DE 13/05/2022; PARECER JURÍDICO Nº 326/2022 - AJU</t>
+          <t>- 3º TERMO ADITIVO (TA) AO CONTRATO 009/2019; PERÍODO: JULHO-AGOSTO; PROCESSO SIGED 018202.001730/2022; EXTRATO DO CONTRATO Nº 009/2019 NO D.O.E. EM 28/06/2019; NAD Nº 32 DE 28/04/2022; PARECER JURÍDI</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2022NE0001590</t>
+          <t>2022NE0001591</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>3449.54</v>
+        <v>1167.84</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -8149,19 +8149,19 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>- 3º TERMO ADITIVO (TA) AO CONTRATO 009/2019; PERÍODO: JULHO-AGOSTO; PROCESSO SIGED 018202.001730/2022; EXTRATO DO CONTRATO Nº 009/2019 NO D.O.E. EM 28/06/2019; NAD Nº 32 DE 28/04/2022; PARECER JURÍDI</t>
+          <t>- 3º TERMO ADITIVO AO CONTRATO Nº 010/2019; VALOR GLOBAL: R$ 14.014,08; VIGÊNCIA: 03/06/2022 - 02/06/2023; NOTA DE AUTORIZAÇÃO DE DESPESAS (NAD) Nº 39 DE 13/05/2022; PARECER JURÍDICO Nº 326/2022 - AJU</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2017NE01343</t>
+          <t>2017NE01344</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>4/2014</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -8170,7 +8170,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>4976.5</v>
+        <v>1947.35</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -8179,19 +8179,19 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Contratação de Serviços de Infraestrutura de TI compreendendo os serviços de Instação, Hospedagem de servidores para ADAF</t>
+          <t>Contratação de Empresa Especializada na prestação de Serviços de execução de Sistemas, CFPP - Cadastro de Folha de Pagamento e Licença de Uso de sistemas de Informação para a disponibilização do siste</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2017NE01344</t>
+          <t>2017NE01343</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>4/2014</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8200,7 +8200,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1947.35</v>
+        <v>4976.5</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -8209,19 +8209,19 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na prestação de Serviços de execução de Sistemas, CFPP - Cadastro de Folha de Pagamento e Licença de Uso de sistemas de Informação para a disponibilização do siste</t>
+          <t>Contratação de Serviços de Infraestrutura de TI compreendendo os serviços de Instação, Hospedagem de servidores para ADAF</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2019NE01056</t>
+          <t>2019NE01054</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>8368.66</v>
+        <v>2624.22</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -8239,19 +8239,19 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e folha de pagamento de pessoal, processar folhas de pagamento e fornecer rel</t>
+          <t>Contratação de empresa para a prestação de serviço de protocolo em plataforma Web (SPROWEB), objetivando o controle e acompanhamento do registro de todos os documentos ou processos do Contratante.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2019NE01057</t>
+          <t>2019NE01055</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>4407.96</v>
+        <v>1312.11</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -8269,19 +8269,19 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de infraestrutura de TI compreendendo os serviços de Instalação, Hospedagem de servidores e suporte em sistemas de informação para esta ADA</t>
+          <t>Contratação de empresa para a prestação de serviço de protocolo em plataforma Web (SPROWEB), objetivando o controle e acompanhamento do registro de todos os documentos ou processos do Contratante.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2019NE01055</t>
+          <t>2019NE01057</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>1312.11</v>
+        <v>4407.96</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -8299,19 +8299,19 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Contratação de empresa para a prestação de serviço de protocolo em plataforma Web (SPROWEB), objetivando o controle e acompanhamento do registro de todos os documentos ou processos do Contratante.</t>
+          <t>Contratação de empresa especializada na prestação de serviço de infraestrutura de TI compreendendo os serviços de Instalação, Hospedagem de servidores e suporte em sistemas de informação para esta ADA</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2019NE01054</t>
+          <t>2019NE01056</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>2624.22</v>
+        <v>8368.66</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Contratação de empresa para a prestação de serviço de protocolo em plataforma Web (SPROWEB), objetivando o controle e acompanhamento do registro de todos os documentos ou processos do Contratante.</t>
+          <t>Contratação de empresa para prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e folha de pagamento de pessoal, processar folhas de pagamento e fornecer rel</t>
         </is>
       </c>
     </row>
@@ -8366,12 +8366,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2019NE00706</t>
+          <t>2019NE00700</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -8380,7 +8380,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>3936.33</v>
+        <v>6606.81</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -8389,19 +8389,19 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Contratação de empresa para a prestação de serviço de protocolo em plataforma Web (SPROWEB), objetivando o controle e acompanhamento do registro de todos os documentos ou processos do Contratante.</t>
+          <t>Contratação de empresa para prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e folha de pagamento de pessoal, processar folhas de pagamento e fornecer rel</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2019NE00700</t>
+          <t>2019NE00706</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8410,7 +8410,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>6606.81</v>
+        <v>3936.33</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -8419,17 +8419,21 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro dos servidores e folha de pagamento de pessoal, processar folhas de pagamento e fornecer rel</t>
+          <t>Contratação de empresa para a prestação de serviço de protocolo em plataforma Web (SPROWEB), objetivando o controle e acompanhamento do registro de todos os documentos ou processos do Contratante.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2015NE00475</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr"/>
+          <t>2015NE00474</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>4/2014</t>
+        </is>
+      </c>
       <c r="C271" t="inlineStr">
         <is>
           <t>01/07/2015</t>
@@ -8445,21 +8449,17 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DE DIVIDA: folha de Informação de Exercício Nº 148/2015,- PRODAM -PROCESSAMENTO DE DADOS DO AMAZONAS</t>
+          <t>RECONHECIMENTO DE DIVIDA: Folha de Informação de Exercício Anteriores Nº 148/2015 - PRODAM - processamento de dados do Amazonas</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2015NE00474</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>4/2014</t>
-        </is>
-      </c>
+          <t>2015NE00475</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
       <c r="C272" t="inlineStr">
         <is>
           <t>01/07/2015</t>
@@ -8475,21 +8475,17 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DE DIVIDA: Folha de Informação de Exercício Anteriores Nº 148/2015 - PRODAM - processamento de dados do Amazonas</t>
+          <t>RECONHECIMENTO DE DIVIDA: folha de Informação de Exercício Nº 148/2015,- PRODAM -PROCESSAMENTO DE DADOS DO AMAZONAS</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2016NE00382</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>4/2014</t>
-        </is>
-      </c>
+          <t>2016NE00381</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr"/>
       <c r="C273" t="inlineStr">
         <is>
           <t>01/06/2016</t>
@@ -8505,7 +8501,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na prestação de Serviços de execução de Sistemas, CFPP - Cadastro de Folha de Pagamento e Licença de Uso de sistemas de Informação para a disponibilização do siste</t>
+          <t>Contratação de empresa especializada nos serviços de processamentos de dados conf 2º termo aditivo ao CT Nº 004/2014</t>
         </is>
       </c>
     </row>
@@ -8542,10 +8538,14 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2016NE00381</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr"/>
+          <t>2016NE00382</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>4/2014</t>
+        </is>
+      </c>
       <c r="C275" t="inlineStr">
         <is>
           <t>01/06/2016</t>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada nos serviços de processamentos de dados conf 2º termo aditivo ao CT Nº 004/2014</t>
+          <t>Contratação de Empresa Especializada na prestação de Serviços de execução de Sistemas, CFPP - Cadastro de Folha de Pagamento e Licença de Uso de sistemas de Informação para a disponibilização do siste</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/ADAF/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/ADAF/dossie.xlsx
@@ -577,7 +577,11 @@
           <t>data_prescricao_proxima</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2028-04-30</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
